--- a/3b. gtsummary to huxtable export test (better captions).xlsx
+++ b/3b. gtsummary to huxtable export test (better captions).xlsx
@@ -93,10 +93,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1,075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,145</t>
+    <t xml:space="preserve">1,087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,147</t>
   </si>
   <si>
     <t xml:space="preserve">1,140</t>
@@ -600,7 +600,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>21</v>
@@ -614,7 +614,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>21</v>
@@ -628,7 +628,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>21</v>
@@ -642,7 +642,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>21</v>
@@ -656,7 +656,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>21</v>
@@ -670,7 +670,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>35</v>
+        <v>34.6</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>21</v>
@@ -684,7 +684,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>21</v>
@@ -698,7 +698,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>21</v>
@@ -712,7 +712,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>21</v>
@@ -726,7 +726,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>21</v>
@@ -740,7 +740,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>21</v>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>21</v>
@@ -796,7 +796,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>21</v>
@@ -810,7 +810,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>21</v>
@@ -824,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>21</v>
@@ -838,7 +838,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>8.4</v>
+        <v>9.2</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>21</v>
@@ -852,7 +852,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>8.3</v>
+        <v>7.6</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>21</v>
@@ -866,7 +866,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>21</v>
@@ -880,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>21.1</v>
+        <v>22.8</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>21</v>
@@ -894,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>21</v>
@@ -908,7 +908,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>21</v>
@@ -936,7 +936,7 @@
         <v>22</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>21</v>
@@ -950,7 +950,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>21</v>
@@ -964,7 +964,7 @@
         <v>22</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>21</v>
@@ -978,7 +978,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>21</v>
@@ -992,7 +992,7 @@
         <v>22</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>21</v>
@@ -1034,7 +1034,7 @@
         <v>22</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>21</v>
@@ -1048,7 +1048,7 @@
         <v>22</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>21</v>
@@ -1062,7 +1062,7 @@
         <v>22</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>21</v>

--- a/3b. gtsummary to huxtable export test (better captions).xlsx
+++ b/3b. gtsummary to huxtable export test (better captions).xlsx
@@ -12,7 +12,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
   <si>
     <t xml:space="preserve">Again, caption provided for testing.</t>
   </si>
@@ -566,44 +569,44 @@
     </row>
     <row r="2" ht="NA" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>4.4</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -611,13 +614,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>2.2</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -625,13 +628,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>5.7</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -639,13 +642,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>11.4</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -653,13 +656,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>10.4</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -667,13 +670,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>34.6</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -681,13 +684,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -695,13 +698,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>9.6</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -709,13 +712,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>6.7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
@@ -723,55 +726,55 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>1.7</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>4.1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" ht="NA" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>2.1</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="NA" customHeight="1">
@@ -779,13 +782,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="NA" customHeight="1">
@@ -793,13 +796,13 @@
         <v>2</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>3.5</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="NA" customHeight="1">
@@ -807,13 +810,13 @@
         <v>3</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>3.5</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="NA" customHeight="1">
@@ -821,13 +824,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>4.7</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="NA" customHeight="1">
@@ -835,13 +838,13 @@
         <v>5</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>9.2</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="NA" customHeight="1">
@@ -849,13 +852,13 @@
         <v>6</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>7.6</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="NA" customHeight="1">
@@ -863,13 +866,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>12.9</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" ht="NA" customHeight="1">
@@ -877,13 +880,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="NA" customHeight="1">
@@ -891,195 +894,195 @@
         <v>9</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>13.3</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" ht="NA" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" ht="NA" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="NA" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>14.5</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" ht="NA" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>47.5</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" ht="NA" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>32.4</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" ht="NA" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>5</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" ht="NA" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" ht="NA" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C34" s="10" t="n">
         <v>48.6</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" ht="NA" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C35" s="10" t="n">
         <v>38.4</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" ht="NA" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C36" s="10" t="n">
         <v>10.5</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" ht="NA" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C37" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
